--- a/data/trans_orig/P6602-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6602-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>215195</t>
+          <t>215515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>251628</t>
+          <t>251927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>166751</t>
+          <t>167726</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>189648</t>
+          <t>190183</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>390440</t>
+          <t>392411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>433440</t>
+          <t>435614</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56581</t>
+          <t>58150</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87738</t>
+          <t>88555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16134</t>
+          <t>16115</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34880</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78162</t>
+          <t>77485</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115159</t>
+          <t>114342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>54665</t>
+          <t>56004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>36173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64667</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18627</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12629</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8591</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23660</t>
+          <t>25484</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>167598</t>
+          <t>165474</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>198563</t>
+          <t>198751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>195524</t>
+          <t>195926</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>214619</t>
+          <t>215448</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>369688</t>
+          <t>369958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>406961</t>
+          <t>407086</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,82%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37416</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63410</t>
+          <t>63569</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14017</t>
+          <t>13718</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31865</t>
+          <t>32036</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54464</t>
+          <t>55556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87921</t>
+          <t>87347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>21060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42801</t>
+          <t>42523</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22981</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43912</t>
+          <t>45826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3719</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15630</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>20081</t>
+          <t>19347</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>104220</t>
+          <t>106270</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142801</t>
+          <t>143029</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>36615</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>131406</t>
+          <t>133931</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>172558</t>
+          <t>173659</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>39,59%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86752</t>
+          <t>86377</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>122325</t>
+          <t>121004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9823</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>100298</t>
+          <t>98355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>137919</t>
+          <t>138946</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>102214</t>
+          <t>104146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>137980</t>
+          <t>138499</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16630</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111893</t>
+          <t>113695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151928</t>
+          <t>152517</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22684</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45298</t>
+          <t>44174</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7441</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48350</t>
+          <t>47771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>222753</t>
+          <t>221080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>274254</t>
+          <t>270904</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>189722</t>
+          <t>187217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>222967</t>
+          <t>221584</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>419281</t>
+          <t>419294</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>482312</t>
+          <t>484439</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,71%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>131199</t>
+          <t>132775</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>178497</t>
+          <t>176457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57206</t>
+          <t>56624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86865</t>
+          <t>87893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200297</t>
+          <t>198932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>255171</t>
+          <t>256368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>205911</t>
+          <t>207270</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>257095</t>
+          <t>255653</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12948</t>
+          <t>13365</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31155</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>225972</t>
+          <t>223306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>281091</t>
+          <t>279750</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>61211</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>95575</t>
+          <t>95569</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4329</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17681</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>67919</t>
+          <t>70447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103850</t>
+          <t>104977</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>40029</t>
+          <t>40243</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>67235</t>
+          <t>66214</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>111650</t>
+          <t>112792</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>141377</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158109</t>
+          <t>158734</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200090</t>
+          <t>201031</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>50,59%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>19920</t>
+          <t>19630</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>41060</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>28313</t>
+          <t>27660</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50606</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>54280</t>
+          <t>53990</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>86582</t>
+          <t>84264</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>56766</t>
+          <t>56053</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83503</t>
+          <t>84038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39971</t>
+          <t>39920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81155</t>
+          <t>82576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>117198</t>
+          <t>117635</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23470</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44178</t>
+          <t>45757</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,49 +3363,49 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>24,72%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>18638</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>11274</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>26918</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>8,78%</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
           <t>12,68%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>18638</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>11166</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>27840</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>13,12%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>51</t>
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>40231</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>67419</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>793753</t>
+          <t>794487</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>882936</t>
+          <t>882437</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,42%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>715506</t>
+          <t>712698</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>775725</t>
+          <t>776740</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1528470</t>
+          <t>1530407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1636992</t>
+          <t>1638485</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,95%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>372357</t>
+          <t>370502</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>443694</t>
+          <t>447352</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>149733</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>196179</t>
+          <t>200366</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>535788</t>
+          <t>534911</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>626704</t>
+          <t>623312</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,28%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>454736</t>
+          <t>454210</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>533478</t>
+          <t>532678</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>53606</t>
+          <t>52096</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>84907</t>
+          <t>86322</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>517389</t>
+          <t>516470</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>608613</t>
+          <t>607685</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>139546</t>
+          <t>137390</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>189671</t>
+          <t>187016</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>52400</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>172380</t>
+          <t>175172</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>229243</t>
+          <t>230649</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>163771</t>
+          <t>165405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198460</t>
+          <t>199655</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119582</t>
+          <t>119543</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145772</t>
+          <t>147695</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,12 +4450,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>292116</t>
+          <t>293063</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>339244</t>
+          <t>338070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -4493,12 +4493,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52832</t>
+          <t>53325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82513</t>
+          <t>81648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,12 +4508,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4528,12 +4528,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>58304</t>
+          <t>59168</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4543,12 +4543,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>92924</t>
+          <t>92577</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131155</t>
+          <t>133111</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -4606,12 +4606,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27519</t>
+          <t>27554</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51507</t>
+          <t>52160</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4621,12 +4621,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5696</t>
+          <t>5074</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19697</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4656,12 +4656,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4676,12 +4676,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35939</t>
+          <t>36894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65377</t>
+          <t>64613</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,02%</t>
         </is>
       </c>
     </row>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25851</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>11766</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4769,12 +4769,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30728</t>
+          <t>32015</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,12 +4804,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -4949,12 +4949,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122268</t>
+          <t>124508</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>158258</t>
+          <t>157211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>110279</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133308</t>
+          <t>133794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4999,12 +4999,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>66,02%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>241454</t>
+          <t>242711</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>282634</t>
+          <t>283256</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44970</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73334</t>
+          <t>73032</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20126</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39620</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>69516</t>
+          <t>69769</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102474</t>
+          <t>102864</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,23%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>32550</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>60779</t>
+          <t>60751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>20946</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>43930</t>
+          <t>43444</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74411</t>
+          <t>74469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,54%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1931</t>
+          <t>1979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11195</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29422</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5518,12 +5518,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64805</t>
+          <t>65454</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>95455</t>
+          <t>96283</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>52610</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74387</t>
+          <t>73618</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>124919</t>
+          <t>125907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163325</t>
+          <t>163107</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5603,12 +5603,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,93%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81610</t>
+          <t>81740</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>112994</t>
+          <t>114177</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>22922</t>
+          <t>23527</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>41437</t>
+          <t>43603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>110632</t>
+          <t>109469</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>148831</t>
+          <t>147400</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52509</t>
+          <t>51458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>80365</t>
+          <t>80950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2211</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13928</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56460</t>
+          <t>56255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87826</t>
+          <t>87369</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24395</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>47342</t>
+          <t>48156</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31767</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57755</t>
+          <t>58276</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86216</t>
+          <t>85613</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>123942</t>
+          <t>123836</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6102,12 +6102,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6122,12 +6122,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>169452</t>
+          <t>174365</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>205623</t>
+          <t>207769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6137,12 +6137,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6157,12 +6157,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>266728</t>
+          <t>266181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>319318</t>
+          <t>321297</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6172,12 +6172,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,33%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>107726</t>
+          <t>109646</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147858</t>
+          <t>148929</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>45706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>74229</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>163457</t>
+          <t>164503</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>211758</t>
+          <t>211626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,2%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94856</t>
+          <t>96647</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>130587</t>
+          <t>131978</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13076</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31138</t>
+          <t>30783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>114699</t>
+          <t>113087</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155890</t>
+          <t>155312</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64044</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>98394</t>
+          <t>99923</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20670</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41880</t>
+          <t>41478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90662</t>
+          <t>92602</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131106</t>
+          <t>130684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3730</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>14083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>72048</t>
+          <t>71226</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>97661</t>
+          <t>98130</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108694</t>
+          <t>108907</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>24137</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44717</t>
+          <t>43892</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47686</t>
+          <t>46580</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>71787</t>
+          <t>73033</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77439</t>
+          <t>78381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111775</t>
+          <t>111030</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>35903</t>
+          <t>36099</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58772</t>
+          <t>60252</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6824</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21701</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46340</t>
+          <t>46719</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75421</t>
+          <t>75842</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>50698</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76224</t>
+          <t>75651</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11478</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>29322</t>
+          <t>30218</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>66511</t>
+          <t>67661</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>101049</t>
+          <t>99582</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,4%</t>
         </is>
       </c>
     </row>
@@ -7225,12 +7225,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>478466</t>
+          <t>481913</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>551632</t>
+          <t>555724</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7240,12 +7240,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>563012</t>
+          <t>560571</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>625035</t>
+          <t>624014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1058141</t>
+          <t>1055602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1154372</t>
+          <t>1156860</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>350935</t>
+          <t>350585</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>420555</t>
+          <t>419527</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>197120</t>
+          <t>197241</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>248769</t>
+          <t>253305</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>562787</t>
+          <t>563294</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>649307</t>
+          <t>653824</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>27,68%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>281115</t>
+          <t>279486</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>344716</t>
+          <t>344046</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>48959</t>
+          <t>47805</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>79520</t>
+          <t>81646</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>338249</t>
+          <t>334155</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>411815</t>
+          <t>409781</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>181290</t>
+          <t>180304</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>235876</t>
+          <t>235981</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52559</t>
+          <t>52762</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>86251</t>
+          <t>84948</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>243065</t>
+          <t>243685</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>305498</t>
+          <t>308595</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -8027,12 +8027,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>131371</t>
+          <t>130326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165578</t>
+          <t>163890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>121393</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148945</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>259137</t>
+          <t>259058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305037</t>
+          <t>305470</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -8140,12 +8140,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68873</t>
+          <t>69297</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98762</t>
+          <t>101225</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40517</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>68162</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118719</t>
+          <t>118616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>159198</t>
+          <t>161113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -8253,12 +8253,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18970</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41416</t>
+          <t>39452</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26850</t>
+          <t>27406</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8303,12 +8303,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33104</t>
+          <t>33379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>60811</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8338,12 +8338,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -8366,12 +8366,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>26472</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8381,12 +8381,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>15564</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8436,12 +8436,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34688</t>
+          <t>36191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8451,12 +8451,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -8596,12 +8596,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97724</t>
+          <t>98110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130386</t>
+          <t>129812</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100322</t>
+          <t>101289</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128030</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,68%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>206634</t>
+          <t>207220</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>251355</t>
+          <t>249354</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8681,12 +8681,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>57,68%</t>
         </is>
       </c>
     </row>
@@ -8709,12 +8709,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44144</t>
+          <t>43016</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71211</t>
+          <t>70929</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32921</t>
+          <t>32303</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55398</t>
+          <t>55105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82671</t>
+          <t>82796</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120945</t>
+          <t>119085</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,55%</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39735</t>
+          <t>40323</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66992</t>
+          <t>67267</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32330</t>
+          <t>32545</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8872,47 +8872,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>17,2%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>73867</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>59302</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>92719</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
           <t>17,09%</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>73867</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>57407</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>90055</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>17,09%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -8935,12 +8935,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13044</t>
+          <t>12159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17164</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20174</t>
+          <t>20690</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41370</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48992</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>74703</t>
+          <t>75620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>33483</t>
+          <t>33229</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>48760</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>72,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>87110</t>
+          <t>86550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120558</t>
+          <t>121027</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9250,12 +9250,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -9278,12 +9278,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>70195</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>99000</t>
+          <t>99778</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29023</t>
+          <t>28603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>89129</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121889</t>
+          <t>122074</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9363,12 +9363,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,16%</t>
         </is>
       </c>
     </row>
@@ -9391,12 +9391,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37618</t>
+          <t>38355</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63377</t>
+          <t>63466</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>993</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9162</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42073</t>
+          <t>41597</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68065</t>
+          <t>67523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9476,12 +9476,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,87%</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12275</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32018</t>
+          <t>32059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5220</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9559,7 +9559,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33818</t>
+          <t>30942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9589,12 +9589,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -9734,12 +9734,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>107264</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>150030</t>
+          <t>148025</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>165154</t>
+          <t>163730</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>202751</t>
+          <t>202610</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9784,12 +9784,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>44,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>284602</t>
+          <t>282699</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>339118</t>
+          <t>339628</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9819,12 +9819,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,84%</t>
         </is>
       </c>
     </row>
@@ -9847,12 +9847,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116704</t>
+          <t>118552</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>157822</t>
+          <t>158024</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9862,12 +9862,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>78421</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>110488</t>
+          <t>111226</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9897,12 +9897,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>206049</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>257366</t>
+          <t>258589</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9932,12 +9932,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,33%</t>
         </is>
       </c>
     </row>
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>94358</t>
+          <t>96167</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>132388</t>
+          <t>133221</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42920</t>
+          <t>43656</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>72668</t>
+          <t>71629</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>148927</t>
+          <t>148225</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>197457</t>
+          <t>195329</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -10073,12 +10073,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>87559</t>
+          <t>87309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127897</t>
+          <t>125126</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>23153</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>47751</t>
+          <t>47369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>116047</t>
+          <t>115787</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160945</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7250</t>
+          <t>7884</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22350</t>
+          <t>22409</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>72052</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>100689</t>
+          <t>101390</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84495</t>
+          <t>82735</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>116482</t>
+          <t>119314</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28316</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>51198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10431,12 +10431,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36719</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59873</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10466,12 +10466,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72764</t>
+          <t>72344</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105451</t>
+          <t>104462</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -10529,12 +10529,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>68568</t>
+          <t>68435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10544,12 +10544,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>16707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>35495</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10579,12 +10579,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63708</t>
+          <t>62492</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>95948</t>
+          <t>96432</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10614,12 +10614,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>71896</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>99894</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10657,12 +10657,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10677,12 +10677,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>25804</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>49327</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10692,12 +10692,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10712,12 +10712,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104585</t>
+          <t>103412</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>142620</t>
+          <t>140742</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10727,12 +10727,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>431176</t>
+          <t>430428</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>498405</t>
+          <t>503593</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>529011</t>
+          <t>528656</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>592967</t>
+          <t>592940</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>975072</t>
+          <t>978632</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1072307</t>
+          <t>1074884</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>370376</t>
+          <t>370830</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>440275</t>
+          <t>440882</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11000,12 +11000,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>232312</t>
+          <t>232281</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>286855</t>
+          <t>285221</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11040,7 +11040,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>618809</t>
+          <t>618962</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>703949</t>
+          <t>706832</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11070,12 +11070,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,89%</t>
         </is>
       </c>
     </row>
@@ -11098,12 +11098,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>265167</t>
+          <t>268039</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>329267</t>
+          <t>332760</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11113,12 +11113,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>105332</t>
+          <t>106448</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>145988</t>
+          <t>149487</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11148,12 +11148,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>390453</t>
+          <t>385695</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>464751</t>
+          <t>461323</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11183,12 +11183,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>218950</t>
+          <t>219361</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>279916</t>
+          <t>280657</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11226,12 +11226,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>70990</t>
+          <t>71743</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>108799</t>
+          <t>109237</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11261,12 +11261,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>299880</t>
+          <t>298908</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>369816</t>
+          <t>368934</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11296,12 +11296,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -11669,32 +11669,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116561</t>
+          <t>129161</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>102781</t>
+          <t>113682</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>143001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11704,32 +11704,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>111139</t>
+          <t>118577</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100992</t>
+          <t>108485</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>119713</t>
+          <t>128292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11739,32 +11739,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>227700</t>
+          <t>247738</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>211325</t>
+          <t>229449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>244815</t>
+          <t>263890</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,95%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,1%</t>
         </is>
       </c>
     </row>
@@ -11782,32 +11782,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>40585</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>53840</t>
+          <t>57202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11817,32 +11817,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21581</t>
+          <t>23634</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30593</t>
+          <t>33265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11852,32 +11852,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>62166</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47285</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77883</t>
+          <t>83376</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,1%</t>
         </is>
       </c>
     </row>
@@ -11895,32 +11895,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6989</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20557</t>
+          <t>23722</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11930,32 +11930,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15891</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11965,32 +11965,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>24235</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30801</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -12008,32 +12008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10606</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5314</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19012</t>
+          <t>25229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12043,32 +12043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14540</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12078,32 +12078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>21865</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>13902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29080</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -12121,17 +12121,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>179857</t>
+          <t>199967</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12156,17 +12156,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>150617</t>
+          <t>161008</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12191,17 +12191,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330474</t>
+          <t>360976</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12238,32 +12238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>100011</t>
+          <t>103801</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>86134</t>
+          <t>88768</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113218</t>
+          <t>116674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -12273,32 +12273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89728</t>
+          <t>95756</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81020</t>
+          <t>86887</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>97428</t>
+          <t>104109</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -12308,32 +12308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>189738</t>
+          <t>199557</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175346</t>
+          <t>181882</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>206238</t>
+          <t>215821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -12351,32 +12351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41579</t>
+          <t>44177</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>32326</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>58058</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12386,32 +12386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26687</t>
+          <t>29210</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12421,32 +12421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>59947</t>
+          <t>64622</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44633</t>
+          <t>49958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73437</t>
+          <t>80710</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,69%</t>
         </is>
       </c>
     </row>
@@ -12464,67 +12464,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11669</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5405</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4213</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1476</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>9118</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
           <t>3,38%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>4029</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1345</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>8084</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12534,32 +12534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>15699</t>
+          <t>16223</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25808</t>
+          <t>26183</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -12577,32 +12577,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2411</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12612,32 +12612,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12647,32 +12647,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10536</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5229</t>
+          <t>5861</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>19044</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -12690,17 +12690,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>160060</t>
+          <t>166884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12725,17 +12725,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115860</t>
+          <t>124610</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12760,17 +12760,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>291494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12807,32 +12807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>277255</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>25284</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>345527</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12842,32 +12842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>31198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>42048</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12877,32 +12877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>309970</t>
+          <t>72118</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>147956</t>
+          <t>57900</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>385413</t>
+          <t>86590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>45,15%</t>
         </is>
       </c>
     </row>
@@ -12920,32 +12920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>48132</t>
+          <t>50977</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>39268</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>153979</t>
+          <t>65247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>45,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12955,32 +12955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4214</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12990,32 +12990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55775</t>
+          <t>58966</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>46930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144658</t>
+          <t>74103</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>38,64%</t>
         </is>
       </c>
     </row>
@@ -13033,32 +13033,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26380</t>
+          <t>30785</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>21606</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85642</t>
+          <t>42398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13068,7 +13068,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -13093,7 +13093,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13103,32 +13103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>32193</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72304</t>
+          <t>44257</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -13146,32 +13146,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>71467</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13181,32 +13181,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13216,32 +13216,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>28507</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65160</t>
+          <t>42238</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -13259,17 +13259,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>372394</t>
+          <t>142088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13294,17 +13294,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44845</t>
+          <t>49696</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13329,17 +13329,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>417239</t>
+          <t>191784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13376,32 +13376,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>59945</t>
+          <t>70497</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>46992</t>
+          <t>55082</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76648</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13411,32 +13411,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>94705</t>
+          <t>102580</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>82350</t>
+          <t>89400</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>106636</t>
+          <t>115343</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13446,32 +13446,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>154651</t>
+          <t>173077</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>134956</t>
+          <t>152180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>174037</t>
+          <t>195575</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -13489,32 +13489,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>79377</t>
+          <t>87144</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62716</t>
+          <t>71544</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96800</t>
+          <t>105367</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13524,32 +13524,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>63382</t>
+          <t>70589</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>58487</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>74602</t>
+          <t>83599</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13559,32 +13559,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>142759</t>
+          <t>157733</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>123862</t>
+          <t>137177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>163888</t>
+          <t>180836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -13602,32 +13602,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>83698</t>
+          <t>93703</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>76807</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>102234</t>
+          <t>113209</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -13637,32 +13637,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>21474</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>14501</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>32082</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -13672,32 +13672,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102698</t>
+          <t>115177</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>84220</t>
+          <t>96409</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>121561</t>
+          <t>137646</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -13715,32 +13715,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25221</t>
+          <t>26497</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49260</t>
+          <t>52858</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13750,32 +13750,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>25569</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12862</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29894</t>
+          <t>36823</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13785,32 +13785,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>55466</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42798</t>
+          <t>49871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>82772</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -13828,17 +13828,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>258655</t>
+          <t>290074</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13863,17 +13863,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>196918</t>
+          <t>220211</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>196918</t>
+          <t>220211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>196918</t>
+          <t>220211</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13898,17 +13898,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>455574</t>
+          <t>510285</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>455574</t>
+          <t>510285</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>455574</t>
+          <t>510285</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13945,32 +13945,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>23292</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14825</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35572</t>
+          <t>37854</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13980,32 +13980,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>44363</t>
+          <t>53017</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>23807</t>
+          <t>43754</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60204</t>
+          <t>64557</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14015,32 +14015,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>67655</t>
+          <t>78709</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>63932</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85203</t>
+          <t>94279</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -14058,32 +14058,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>44175</t>
+          <t>49580</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>32996</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60028</t>
+          <t>64162</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14093,32 +14093,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>53573</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>44151</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>59621</t>
+          <t>63099</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14128,32 +14128,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>88686</t>
+          <t>103153</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60177</t>
+          <t>86796</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>109252</t>
+          <t>120590</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,29%</t>
         </is>
       </c>
     </row>
@@ -14171,32 +14171,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>36695</t>
+          <t>47862</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26686</t>
+          <t>35245</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50147</t>
+          <t>63825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14206,32 +14206,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>60209</t>
+          <t>30580</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>30825</t>
+          <t>22619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>107494</t>
+          <t>40760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,01%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14241,32 +14241,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>78442</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>158616</t>
+          <t>95745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>29,61%</t>
         </is>
       </c>
     </row>
@@ -14284,32 +14284,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28112</t>
+          <t>45615</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>32937</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39512</t>
+          <t>60573</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -14319,32 +14319,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>13766</t>
+          <t>17450</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -14354,32 +14354,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>41878</t>
+          <t>63065</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27425</t>
+          <t>46830</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>57959</t>
+          <t>80603</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -14397,17 +14397,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>132274</t>
+          <t>168750</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14432,17 +14432,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>162849</t>
+          <t>154620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14467,17 +14467,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>323369</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14514,32 +14514,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>577064</t>
+          <t>364274</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>414492</t>
+          <t>331945</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>827748</t>
+          <t>401144</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14549,32 +14549,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>372652</t>
+          <t>406926</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>301126</t>
+          <t>382105</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>401042</t>
+          <t>429300</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14584,32 +14584,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>949715</t>
+          <t>771199</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>796733</t>
+          <t>729345</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1280450</t>
+          <t>817008</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>48,69%</t>
         </is>
       </c>
     </row>
@@ -14627,32 +14627,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>253849</t>
+          <t>275382</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>135295</t>
+          <t>244228</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>339720</t>
+          <t>308326</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14662,32 +14662,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>155484</t>
+          <t>176230</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>128180</t>
+          <t>156035</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>176638</t>
+          <t>197927</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14697,32 +14697,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>409333</t>
+          <t>451612</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>247404</t>
+          <t>417749</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>491274</t>
+          <t>493231</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -14740,32 +14740,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>170548</t>
+          <t>198548</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>86241</t>
+          <t>171395</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>228954</t>
+          <t>227097</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14775,32 +14775,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>94048</t>
+          <t>67722</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>59191</t>
+          <t>54688</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212220</t>
+          <t>83317</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14810,32 +14810,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>264595</t>
+          <t>266270</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>169684</t>
+          <t>235482</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>351402</t>
+          <t>298998</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -14853,32 +14853,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>101781</t>
+          <t>129559</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>49442</t>
+          <t>107714</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>140643</t>
+          <t>156227</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14888,32 +14888,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>48906</t>
+          <t>59268</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37103</t>
+          <t>46689</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>76324</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14923,32 +14923,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>150688</t>
+          <t>188828</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93911</t>
+          <t>161024</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>184860</t>
+          <t>222432</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -14966,17 +14966,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1103241</t>
+          <t>967763</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -15001,17 +15001,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>671090</t>
+          <t>710146</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>671090</t>
+          <t>710146</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>671090</t>
+          <t>710146</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15036,17 +15036,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1774331</t>
+          <t>1677908</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1774331</t>
+          <t>1677908</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1774331</t>
+          <t>1677908</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
